--- a/src/data/OpenCartTestData.xlsx
+++ b/src/data/OpenCartTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PW2026_Framework_OpenCart\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CF0487-F0D0-4398-B020-B75A57971FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A207B5C-DAF4-43C6-907D-8901D136CFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,13 +39,13 @@
     <t>wrong123</t>
   </si>
   <si>
-    <t>pw123</t>
-  </si>
-  <si>
     <t>pwbatchtest@open.com</t>
   </si>
   <si>
     <t>pw124</t>
+  </si>
+  <si>
+    <t>pw4321</t>
   </si>
 </sst>
 </file>
@@ -377,7 +377,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -398,18 +399,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -417,6 +418,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{50891979-9C79-40A2-8B52-E7B890DE39F9}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{A19617F4-C566-4033-B6D0-ADB17524F26C}"/>
     <hyperlink ref="A3" r:id="rId3" xr:uid="{92FAE77A-628F-41B7-8C58-BE93CE97B8E9}"/>
+    <hyperlink ref="B3" r:id="rId4" display="pw123@432" xr:uid="{9CEA22A4-243E-4813-B0D0-1104D3399531}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
